--- a/InputData/indst/MHV/Methane Heating Value.xlsx
+++ b/InputData/indst/MHV/Methane Heating Value.xlsx
@@ -1,17 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27021"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_98092BC3891B0A8B0A6B02BBAF642D55B310926D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="135" windowWidth="25875" windowHeight="12855"/>
+    <workbookView xWindow="480" yWindow="135" windowWidth="25875" windowHeight="12855" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
     <sheet name="MHV" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -27,12 +44,12 @@
     <t>Engineering Toolbox</t>
   </si>
   <si>
+    <t>Fuel Gases Heating Values</t>
+  </si>
+  <si>
     <t>http://www.engineeringtoolbox.com/heating-values-fuel-gases-d_823.html</t>
   </si>
   <si>
-    <t>Fuel Gases Heating Values</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -57,35 +74,35 @@
     <t>the lower heating value.</t>
   </si>
   <si>
+    <t>Higher (gross) heating value</t>
+  </si>
+  <si>
+    <t>Lower (net) heating value</t>
+  </si>
+  <si>
+    <t>BTU/lb</t>
+  </si>
+  <si>
+    <t>grams/lb</t>
+  </si>
+  <si>
+    <t>BTU/g</t>
+  </si>
+  <si>
     <t>Methane</t>
   </si>
   <si>
     <t>Heating Value (BTU/g)</t>
   </si>
-  <si>
-    <t>Higher (gross) heating value</t>
-  </si>
-  <si>
-    <t>Lower (net) heating value</t>
-  </si>
-  <si>
-    <t>BTU/lb</t>
-  </si>
-  <si>
-    <t>grams/lb</t>
-  </si>
-  <si>
-    <t>BTU/g</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,14 +157,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -185,7 +205,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -257,7 +277,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -430,16 +450,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -447,57 +467,57 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="B4" s="2">
         <v>2016</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -509,26 +529,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="29.42578125" customWidth="1"/>
     <col min="3" max="3" width="33.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>17</v>
       </c>
       <c r="B2">
         <v>23811</v>
@@ -537,9 +557,9 @@
         <v>21433</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4">
         <v>453.59199999999998</v>
@@ -548,9 +568,9 @@
         <v>453.59199999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3">
         <f>B2/B3</f>
@@ -567,25 +587,25 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="21.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3">
         <f>Data!B4</f>
@@ -595,4 +615,175 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{804C7FCE-F867-4128-AF1C-904B6C098DFB}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0431980-2985-48A7-A8D4-793B65E4FE10}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97D26E22-C6C1-4758-AB52-8DA79DD0A071}"/>
 </file>